--- a/Presencas_Nexus_Mentoria.xlsx
+++ b/Presencas_Nexus_Mentoria.xlsx
@@ -33969,13 +33969,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8F8960B-EEE1-4F32-9D9F-43F24CC4FD0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F119103-E066-4D59-BDB9-FD853574F39D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43CA30F1-6B5F-45CD-A0E2-239CDB585B21}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F181C615-C32F-490D-8F47-8963940BCFAF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F2C79A1-E0E1-453D-BB15-93E31A71F255}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD201D5C-B064-4F6B-89AF-0C252BF7D6E0}"/>
 </file>